--- a/other/class_timetable/newXlsx.xlsx
+++ b/other/class_timetable/newXlsx.xlsx
@@ -433,7 +433,7 @@
         <v>10/03/2024</v>
       </c>
       <c r="C2" t="str">
-        <v>08:20</v>
+        <v>08:05</v>
       </c>
       <c r="D2" t="str">
         <v>10/03/2024</v>
@@ -459,7 +459,7 @@
         <v>17/03/2024</v>
       </c>
       <c r="C3" t="str">
-        <v>08:20</v>
+        <v>06:20</v>
       </c>
       <c r="D3" t="str">
         <v>17/03/2024</v>
@@ -485,7 +485,7 @@
         <v>24/03/2024</v>
       </c>
       <c r="C4" t="str">
-        <v>08:20</v>
+        <v>08:05</v>
       </c>
       <c r="D4" t="str">
         <v>24/03/2024</v>
@@ -511,7 +511,7 @@
         <v>06/04/2024</v>
       </c>
       <c r="C5" t="str">
-        <v>08:20</v>
+        <v>08:05</v>
       </c>
       <c r="D5" t="str">
         <v>06/04/2024</v>
@@ -537,7 +537,7 @@
         <v>14/04/2024</v>
       </c>
       <c r="C6" t="str">
-        <v>08:20</v>
+        <v>08:05</v>
       </c>
       <c r="D6" t="str">
         <v>14/04/2024</v>
@@ -563,7 +563,7 @@
         <v>21/04/2024</v>
       </c>
       <c r="C7" t="str">
-        <v>08:20</v>
+        <v>06:20</v>
       </c>
       <c r="D7" t="str">
         <v>21/04/2024</v>
@@ -589,7 +589,7 @@
         <v>27/04/2024</v>
       </c>
       <c r="C8" t="str">
-        <v>08:20</v>
+        <v>08:05</v>
       </c>
       <c r="D8" t="str">
         <v>27/04/2024</v>
@@ -615,7 +615,7 @@
         <v>19/05/2024</v>
       </c>
       <c r="C9" t="str">
-        <v>08:20</v>
+        <v>08:05</v>
       </c>
       <c r="D9" t="str">
         <v>19/05/2024</v>
@@ -641,7 +641,7 @@
         <v>26/05/2024</v>
       </c>
       <c r="C10" t="str">
-        <v>08:20</v>
+        <v>08:05</v>
       </c>
       <c r="D10" t="str">
         <v>26/05/2024</v>
@@ -667,7 +667,7 @@
         <v>09/06/2024</v>
       </c>
       <c r="C11" t="str">
-        <v>08:20</v>
+        <v>08:05</v>
       </c>
       <c r="D11" t="str">
         <v>09/06/2024</v>
@@ -693,7 +693,7 @@
         <v>16/06/2024</v>
       </c>
       <c r="C12" t="str">
-        <v>08:20</v>
+        <v>06:20</v>
       </c>
       <c r="D12" t="str">
         <v>16/06/2024</v>
@@ -719,7 +719,7 @@
         <v>23/06/2024</v>
       </c>
       <c r="C13" t="str">
-        <v>08:20</v>
+        <v>08:05</v>
       </c>
       <c r="D13" t="str">
         <v>23/06/2024</v>
@@ -745,7 +745,7 @@
         <v>29/03/2024</v>
       </c>
       <c r="C14" t="str">
-        <v>18:15</v>
+        <v>18:00</v>
       </c>
       <c r="D14" t="str">
         <v>29/03/2024</v>
@@ -771,7 +771,7 @@
         <v>10/05/2024</v>
       </c>
       <c r="C15" t="str">
-        <v>18:15</v>
+        <v>18:00</v>
       </c>
       <c r="D15" t="str">
         <v>10/05/2024</v>
@@ -797,7 +797,7 @@
         <v>31/05/2024</v>
       </c>
       <c r="C16" t="str">
-        <v>18:15</v>
+        <v>18:00</v>
       </c>
       <c r="D16" t="str">
         <v>31/05/2024</v>
@@ -823,7 +823,7 @@
         <v>31/03/2024</v>
       </c>
       <c r="C17" t="str">
-        <v>08:20</v>
+        <v>06:20</v>
       </c>
       <c r="D17" t="str">
         <v>31/03/2024</v>
@@ -849,7 +849,7 @@
         <v>12/05/2024</v>
       </c>
       <c r="C18" t="str">
-        <v>08:20</v>
+        <v>06:20</v>
       </c>
       <c r="D18" t="str">
         <v>12/05/2024</v>
@@ -875,7 +875,7 @@
         <v>02/06/2024</v>
       </c>
       <c r="C19" t="str">
-        <v>08:20</v>
+        <v>06:20</v>
       </c>
       <c r="D19" t="str">
         <v>02/06/2024</v>
@@ -901,7 +901,7 @@
         <v>10/03/2024</v>
       </c>
       <c r="C20" t="str">
-        <v>18:15</v>
+        <v>18:00</v>
       </c>
       <c r="D20" t="str">
         <v>10/03/2024</v>
@@ -927,7 +927,7 @@
         <v>17/03/2024</v>
       </c>
       <c r="C21" t="str">
-        <v>18:15</v>
+        <v>18:00</v>
       </c>
       <c r="D21" t="str">
         <v>17/03/2024</v>
@@ -953,7 +953,7 @@
         <v>24/03/2024</v>
       </c>
       <c r="C22" t="str">
-        <v>18:15</v>
+        <v>18:00</v>
       </c>
       <c r="D22" t="str">
         <v>24/03/2024</v>
@@ -979,7 +979,7 @@
         <v>06/04/2024</v>
       </c>
       <c r="C23" t="str">
-        <v>18:15</v>
+        <v>18:00</v>
       </c>
       <c r="D23" t="str">
         <v>06/04/2024</v>
@@ -1005,7 +1005,7 @@
         <v>14/04/2024</v>
       </c>
       <c r="C24" t="str">
-        <v>18:15</v>
+        <v>18:00</v>
       </c>
       <c r="D24" t="str">
         <v>14/04/2024</v>
@@ -1031,7 +1031,7 @@
         <v>21/04/2024</v>
       </c>
       <c r="C25" t="str">
-        <v>18:15</v>
+        <v>18:00</v>
       </c>
       <c r="D25" t="str">
         <v>21/04/2024</v>
@@ -1057,7 +1057,7 @@
         <v>27/04/2024</v>
       </c>
       <c r="C26" t="str">
-        <v>18:15</v>
+        <v>18:00</v>
       </c>
       <c r="D26" t="str">
         <v>27/04/2024</v>
@@ -1083,7 +1083,7 @@
         <v>19/05/2024</v>
       </c>
       <c r="C27" t="str">
-        <v>18:15</v>
+        <v>18:00</v>
       </c>
       <c r="D27" t="str">
         <v>19/05/2024</v>
@@ -1109,7 +1109,7 @@
         <v>26/05/2024</v>
       </c>
       <c r="C28" t="str">
-        <v>18:15</v>
+        <v>18:00</v>
       </c>
       <c r="D28" t="str">
         <v>26/05/2024</v>
@@ -1135,7 +1135,7 @@
         <v>09/06/2024</v>
       </c>
       <c r="C29" t="str">
-        <v>18:15</v>
+        <v>18:00</v>
       </c>
       <c r="D29" t="str">
         <v>09/06/2024</v>
@@ -1161,7 +1161,7 @@
         <v>16/06/2024</v>
       </c>
       <c r="C30" t="str">
-        <v>18:15</v>
+        <v>18:00</v>
       </c>
       <c r="D30" t="str">
         <v>16/06/2024</v>
@@ -1187,7 +1187,7 @@
         <v>23/06/2024</v>
       </c>
       <c r="C31" t="str">
-        <v>18:15</v>
+        <v>18:00</v>
       </c>
       <c r="D31" t="str">
         <v>23/06/2024</v>
@@ -1213,7 +1213,7 @@
         <v>24/03/2024</v>
       </c>
       <c r="C32" t="str">
-        <v>12:20</v>
+        <v>12:05</v>
       </c>
       <c r="D32" t="str">
         <v>24/03/2024</v>
@@ -1239,7 +1239,7 @@
         <v>14/04/2024</v>
       </c>
       <c r="C33" t="str">
-        <v>12:20</v>
+        <v>12:05</v>
       </c>
       <c r="D33" t="str">
         <v>14/04/2024</v>
@@ -1265,7 +1265,7 @@
         <v>23/03/2024</v>
       </c>
       <c r="C34" t="str">
-        <v>12:20</v>
+        <v>12:05</v>
       </c>
       <c r="D34" t="str">
         <v>23/03/2024</v>
@@ -1291,7 +1291,7 @@
         <v>13/04/2024</v>
       </c>
       <c r="C35" t="str">
-        <v>12:20</v>
+        <v>12:05</v>
       </c>
       <c r="D35" t="str">
         <v>13/04/2024</v>
@@ -1317,7 +1317,7 @@
         <v>27/04/2024</v>
       </c>
       <c r="C36" t="str">
-        <v>12:20</v>
+        <v>12:05</v>
       </c>
       <c r="D36" t="str">
         <v>27/04/2024</v>
